--- a/umaData.xlsx
+++ b/umaData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f3d4df9b9e53cc53/デスクトップ/Python_game/py_GUI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\udonp\py_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3739F7F-023F-40B5-85EC-36CAB39C1F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43352127-9B64-48EE-87E8-B9907F194217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1665" windowWidth="25995" windowHeight="19935" xr2:uid="{8743B8C8-B4DD-47C9-A4DA-56F961C3D928}"/>
+    <workbookView xWindow="315" yWindow="825" windowWidth="25995" windowHeight="19935" xr2:uid="{8743B8C8-B4DD-47C9-A4DA-56F961C3D928}"/>
   </bookViews>
   <sheets>
     <sheet name="保存" sheetId="1" r:id="rId1"/>

--- a/umaData.xlsx
+++ b/umaData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\udonp\py_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f3d4df9b9e53cc53/デスクトップ/Python_game/py_GUI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43352127-9B64-48EE-87E8-B9907F194217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE36002B-7426-4096-89FB-9AA9C692F4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="825" windowWidth="25995" windowHeight="19935" xr2:uid="{8743B8C8-B4DD-47C9-A4DA-56F961C3D928}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25995" windowHeight="19935" xr2:uid="{A1688860-B8C1-4BB2-AD78-FC75B717E70D}"/>
   </bookViews>
   <sheets>
     <sheet name="保存" sheetId="1" r:id="rId1"/>
@@ -2658,7 +2658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4731D491-2601-452B-BF57-6E798F806322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF37B57-8E7A-426B-A839-5BC05F77E6D4}">
   <sheetPr codeName="shtBackUpData"/>
   <dimension ref="A1:AN596"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -59119,6 +59119,12 @@
       <c r="Z581" s="8" t="s">
         <v>128</v>
       </c>
+      <c r="AA581">
+        <v>12</v>
+      </c>
+      <c r="AB581">
+        <v>15</v>
+      </c>
       <c r="AC581" t="s">
         <v>27</v>
       </c>
@@ -59220,6 +59226,12 @@
       <c r="Z582" s="8" t="s">
         <v>105</v>
       </c>
+      <c r="AA582">
+        <v>11</v>
+      </c>
+      <c r="AB582">
+        <v>10</v>
+      </c>
       <c r="AC582" t="s">
         <v>106</v>
       </c>
@@ -59312,6 +59324,12 @@
       <c r="Z583" s="8" t="s">
         <v>301</v>
       </c>
+      <c r="AA583">
+        <v>5</v>
+      </c>
+      <c r="AB583">
+        <v>9</v>
+      </c>
       <c r="AC583" t="s">
         <v>27</v>
       </c>
@@ -59404,6 +59422,12 @@
       <c r="Z584" s="8" t="s">
         <v>96</v>
       </c>
+      <c r="AA584">
+        <v>3</v>
+      </c>
+      <c r="AB584">
+        <v>2</v>
+      </c>
       <c r="AC584" t="s">
         <v>27</v>
       </c>
@@ -59496,6 +59520,12 @@
       <c r="Z585" s="8" t="s">
         <v>124</v>
       </c>
+      <c r="AA585">
+        <v>10</v>
+      </c>
+      <c r="AB585">
+        <v>4</v>
+      </c>
       <c r="AC585" t="s">
         <v>27</v>
       </c>
@@ -59588,6 +59618,12 @@
       <c r="Z586" s="8" t="s">
         <v>126</v>
       </c>
+      <c r="AA586">
+        <v>2</v>
+      </c>
+      <c r="AB586">
+        <v>3</v>
+      </c>
       <c r="AC586" t="s">
         <v>27</v>
       </c>
@@ -59689,6 +59725,12 @@
       <c r="Z587" s="8" t="s">
         <v>113</v>
       </c>
+      <c r="AA587">
+        <v>15</v>
+      </c>
+      <c r="AB587">
+        <v>6</v>
+      </c>
       <c r="AC587" t="s">
         <v>27</v>
       </c>
@@ -59781,6 +59823,12 @@
       <c r="Z588" s="8" t="s">
         <v>265</v>
       </c>
+      <c r="AA588">
+        <v>14</v>
+      </c>
+      <c r="AB588">
+        <v>7</v>
+      </c>
       <c r="AC588" t="s">
         <v>106</v>
       </c>
@@ -59882,6 +59930,12 @@
       <c r="Z589" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="AA589">
+        <v>7</v>
+      </c>
+      <c r="AB589">
+        <v>11</v>
+      </c>
       <c r="AC589" t="s">
         <v>666</v>
       </c>
@@ -59974,6 +60028,12 @@
       <c r="Z590" s="8" t="s">
         <v>115</v>
       </c>
+      <c r="AA590">
+        <v>9</v>
+      </c>
+      <c r="AB590">
+        <v>14</v>
+      </c>
       <c r="AC590" t="s">
         <v>106</v>
       </c>
@@ -60066,6 +60126,12 @@
       <c r="Z591" s="8" t="s">
         <v>103</v>
       </c>
+      <c r="AA591">
+        <v>8</v>
+      </c>
+      <c r="AB591">
+        <v>8</v>
+      </c>
       <c r="AC591" t="s">
         <v>27</v>
       </c>
@@ -60158,6 +60224,12 @@
       <c r="Z592" s="8" t="s">
         <v>111</v>
       </c>
+      <c r="AA592">
+        <v>6</v>
+      </c>
+      <c r="AB592">
+        <v>5</v>
+      </c>
       <c r="AC592" t="s">
         <v>27</v>
       </c>
@@ -60259,6 +60331,12 @@
       <c r="Z593" s="8" t="s">
         <v>165</v>
       </c>
+      <c r="AA593">
+        <v>13</v>
+      </c>
+      <c r="AB593">
+        <v>12</v>
+      </c>
       <c r="AC593" t="s">
         <v>27</v>
       </c>
@@ -60360,6 +60438,12 @@
       <c r="Z594" s="8" t="s">
         <v>250</v>
       </c>
+      <c r="AA594">
+        <v>4</v>
+      </c>
+      <c r="AB594">
+        <v>13</v>
+      </c>
       <c r="AC594" t="s">
         <v>27</v>
       </c>
@@ -60451,6 +60535,12 @@
       </c>
       <c r="Z595" s="8" t="s">
         <v>119</v>
+      </c>
+      <c r="AA595">
+        <v>1</v>
+      </c>
+      <c r="AB595">
+        <v>1</v>
       </c>
       <c r="AC595" t="s">
         <v>27</v>
